--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -370,7 +370,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -461,7 +461,7 @@
     <t>dueDateOfNextDose</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_DueDateOfNextDose}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_DueDateOfNextDose|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>manufacturedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_ManufacturedDate}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_ManufacturedDate|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -497,7 +497,7 @@
     <t>certificatedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_CertificatedDate}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_CertificatedDate|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -608,7 +608,7 @@
     <t>ワクチンが投与されなかった理由。 / The reason why a vaccine was not administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -629,7 +629,7 @@
     <t>全てのターミノロジがこのパターンに当てはまるわけではない。モデルによってはCodeableConceptではなく，独自構造でCodingを直接指定して文書やコーディング，その解釈や事前条件や事後条件との関連について示される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_Immunization_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_Immunization_VS|1.1.0a</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -650,7 +650,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>Immunization.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -787,7 +787,7 @@
     <t>主要なソースからのものではないレコードのデータのソース。 / The source of the data for a record which is not from a primary source.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-origin</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-origin|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=INF].role[classCode=PAT] (this syntax for self-reported) .participation[typeCode=INF].role[classCode=LIC] (this syntax for health care professional) .participation[typeCode=INF].role[classCode=PRS] (this syntax for family member)</t>
@@ -796,7 +796,7 @@
     <t>Immunization.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -821,7 +821,7 @@
     <t>Immunization.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -887,7 +887,7 @@
     <t>ワクチンが接種された身体部位</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -911,7 +911,7 @@
     <t>ワクチンが投与されたルート。 / The route by which the vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-route|4.0.1</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -926,7 +926,7 @@
     <t>Immunization.doseQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1024,7 +1024,7 @@
     <t>予防接種イベントで開業医または組織が果たす役割。 / The role a practitioner or organization plays in the immunization event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-function</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1036,7 +1036,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1092,7 +1092,7 @@
     <t>ワクチンが投与された理由。 / The reason why a vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1104,7 +1104,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>用量がサブポテントと見なされる理由。 / The reason why a dose is considered to be subpotent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason|4.0.1</t>
   </si>
   <si>
     <t>Immunization.education</t>
@@ -1229,7 +1229,7 @@
     <t>患者の予防接種プログラムの適格性。 / The patient's eligibility for a vaccation program.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility|4.0.1</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 64994-7</t>
@@ -1247,7 +1247,7 @@
     <t>投与されたワクチンの購入に使用される資金源。 / The source of funding used to purchase the vaccine administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source|4.0.1</t>
   </si>
   <si>
     <t>Immunization.reaction</t>
@@ -1292,7 +1292,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1353,7 +1353,7 @@
     <t>Immunization.protocolApplied.authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1375,7 +1375,7 @@
     <t>ワクチン予防可能な疾患用量が投与されています。 / The vaccine preventable disease the dose is being administered for.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
@@ -1717,7 +1717,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="175.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1732,7 +1732,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.81640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.46484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -370,7 +370,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -461,7 +461,7 @@
     <t>dueDateOfNextDose</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_DueDateOfNextDose|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_DueDateOfNextDose}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>manufacturedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_ManufacturedDate|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_ManufacturedDate}
 </t>
   </si>
   <si>
@@ -497,7 +497,7 @@
     <t>certificatedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_CertificatedDate|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Immunization_CertificatedDate}
 </t>
   </si>
   <si>
@@ -608,7 +608,7 @@
     <t>ワクチンが投与されなかった理由。 / The reason why a vaccine was not administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -629,7 +629,7 @@
     <t>全てのターミノロジがこのパターンに当てはまるわけではない。モデルによってはCodeableConceptではなく，独自構造でCodingを直接指定して文書やコーディング，その解釈や事前条件や事後条件との関連について示される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_Immunization_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_Immunization_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -650,7 +650,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>Immunization.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -787,7 +787,7 @@
     <t>主要なソースからのものではないレコードのデータのソース。 / The source of the data for a record which is not from a primary source.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-origin|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-origin</t>
   </si>
   <si>
     <t>.participation[typeCode=INF].role[classCode=PAT] (this syntax for self-reported) .participation[typeCode=INF].role[classCode=LIC] (this syntax for health care professional) .participation[typeCode=INF].role[classCode=PRS] (this syntax for family member)</t>
@@ -796,7 +796,7 @@
     <t>Immunization.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -821,7 +821,7 @@
     <t>Immunization.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -887,7 +887,7 @@
     <t>ワクチンが接種された身体部位</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -911,7 +911,7 @@
     <t>ワクチンが投与されたルート。 / The route by which the vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-route|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -926,7 +926,7 @@
     <t>Immunization.doseQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1024,7 +1024,7 @@
     <t>予防接種イベントで開業医または組織が果たす役割。 / The role a practitioner or organization plays in the immunization event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-function</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1036,7 +1036,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1092,7 +1092,7 @@
     <t>ワクチンが投与された理由。 / The reason why a vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-reason</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1104,7 +1104,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>用量がサブポテントと見なされる理由。 / The reason why a dose is considered to be subpotent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason</t>
   </si>
   <si>
     <t>Immunization.education</t>
@@ -1229,7 +1229,7 @@
     <t>患者の予防接種プログラムの適格性。 / The patient's eligibility for a vaccation program.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 64994-7</t>
@@ -1247,7 +1247,7 @@
     <t>投与されたワクチンの購入に使用される資金源。 / The source of funding used to purchase the vaccine administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source</t>
   </si>
   <si>
     <t>Immunization.reaction</t>
@@ -1292,7 +1292,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(Observation)
 </t>
   </si>
   <si>
@@ -1353,7 +1353,7 @@
     <t>Immunization.protocolApplied.authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1375,7 +1375,7 @@
     <t>ワクチン予防可能な疾患用量が投与されています。 / The vaccine preventable disease the dose is being administered for.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
@@ -1717,7 +1717,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="175.3828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1732,7 +1732,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.81640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.95703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.46484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
